--- a/codespace/DetroitRiverCase/results/ch4_fw2_c1_bray_curtis_dissimilarity_matrix.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_c1_bray_curtis_dissimilarity_matrix.xlsx
@@ -932,10 +932,10 @@
         <v>0.9222257067335693</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8126163749580785</v>
+        <v>0.6007713150584472</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.965661265609231</v>
+        <v>0.9658225991281506</v>
       </c>
     </row>
     <row r="3">
@@ -1125,10 +1125,10 @@
         <v>0.7104710471047103</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7105156500519092</v>
+        <v>0.4439538562426334</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.8648586204675313</v>
+        <v>0.8703376598188658</v>
       </c>
     </row>
     <row r="4">
@@ -1318,10 +1318,10 @@
         <v>0.6081292339760294</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5757575960531872</v>
+        <v>0.4281125412822164</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.7550440368433465</v>
+        <v>0.7637332265920213</v>
       </c>
     </row>
     <row r="5">
@@ -1511,10 +1511,10 @@
         <v>0.6148999515336147</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5810291529141534</v>
+        <v>0.3333806415686714</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.7588222585992722</v>
+        <v>0.7680467338693502</v>
       </c>
     </row>
     <row r="6">
@@ -1704,10 +1704,10 @@
         <v>0.6006283320639754</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.503280834611722</v>
+        <v>0.2252135626550993</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.7474475440137035</v>
+        <v>0.7540285041162277</v>
       </c>
     </row>
     <row r="7">
@@ -1897,10 +1897,10 @@
         <v>0.4467821782178218</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.3693210387111948</v>
+        <v>0.3434639101494442</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5796524941324501</v>
+        <v>0.5785493928894765</v>
       </c>
     </row>
     <row r="8">
@@ -2090,10 +2090,10 @@
         <v>0.7678533810827891</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7941310827725341</v>
+        <v>0.5091305539738301</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.9238833544581779</v>
+        <v>0.9276382276481304</v>
       </c>
     </row>
     <row r="9">
@@ -2283,10 +2283,10 @@
         <v>0.610773003905895</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5784256849028733</v>
+        <v>0.3630207320158721</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7634614999341712</v>
+        <v>0.7693816410829479</v>
       </c>
     </row>
     <row r="10">
@@ -2476,10 +2476,10 @@
         <v>0.976830853476409</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8769059414335556</v>
+        <v>0.6621496074165137</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.9563912421766991</v>
+        <v>0.9424874577599968</v>
       </c>
     </row>
     <row r="11">
@@ -2669,10 +2669,10 @@
         <v>0.8271395632713956</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.8432888125440029</v>
+        <v>0.5871229431262491</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.9585821951327957</v>
+        <v>0.9589827278410081</v>
       </c>
     </row>
     <row r="12">
@@ -2862,10 +2862,10 @@
         <v>0.8217821782178216</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8541405226390921</v>
+        <v>0.5727087638991687</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.9807048317639048</v>
+        <v>0.9801371943952442</v>
       </c>
     </row>
     <row r="13">
@@ -3055,10 +3055,10 @@
         <v>0.524348353202667</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5116001284635748</v>
+        <v>0.4772028133611028</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6336615415191472</v>
+        <v>0.6459667350382698</v>
       </c>
     </row>
     <row r="14">
@@ -3248,10 +3248,10 @@
         <v>0.1881188118811884</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5830186234562988</v>
+        <v>0.8104170651139526</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.1150644906859261</v>
+        <v>0.1177723509016278</v>
       </c>
     </row>
     <row r="15">
@@ -3441,10 +3441,10 @@
         <v>0.3999999999999999</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5626731533732837</v>
+        <v>0.6501217464656187</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.3741821563831103</v>
+        <v>0.393633069970706</v>
       </c>
     </row>
     <row r="16">
@@ -3634,10 +3634,10 @@
         <v>0.5027689209598923</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.4610162540527594</v>
+        <v>0.6320260132683851</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.605269373365392</v>
+        <v>0.6186684250987838</v>
       </c>
     </row>
     <row r="17">
@@ -3827,10 +3827,10 @@
         <v>0.184563685793197</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5255939536785866</v>
+        <v>0.7735846025015206</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.1217062162351357</v>
+        <v>0.1243090843981093</v>
       </c>
     </row>
     <row r="18">
@@ -4020,10 +4020,10 @@
         <v>0.2499999999999999</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5771036939990857</v>
+        <v>0.8040720585337532</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.2259912691954164</v>
+        <v>0.2497463790003698</v>
       </c>
     </row>
     <row r="19">
@@ -4213,10 +4213,10 @@
         <v>0.1485148514851488</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.52925271130187</v>
+        <v>0.751593535702188</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.108258984302873</v>
+        <v>0.1088983586525853</v>
       </c>
     </row>
     <row r="20">
@@ -4406,10 +4406,10 @@
         <v>0.4959494033694555</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.4432083344818188</v>
+        <v>0.6857241690110846</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.4396310455600839</v>
+        <v>0.4193551684938284</v>
       </c>
     </row>
     <row r="21">
@@ -4599,10 +4599,10 @@
         <v>0.1381188118811884</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.5112923827334412</v>
+        <v>0.7518838901754366</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.1051970899999074</v>
+        <v>0.1095193965456086</v>
       </c>
     </row>
     <row r="22">
@@ -4792,10 +4792,10 @@
         <v>0.1747572399718615</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.5511048247580528</v>
+        <v>0.79679102423583</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.06984088436525092</v>
+        <v>0.07411361563918045</v>
       </c>
     </row>
     <row r="23">
@@ -4985,10 +4985,10 @@
         <v>0.2740366406323382</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.4182177624849774</v>
+        <v>0.661350932122268</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.2061751512231627</v>
+        <v>0.2059302434166669</v>
       </c>
     </row>
     <row r="24">
@@ -5178,10 +5178,10 @@
         <v>0.9635019274060204</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.8901538770551417</v>
+        <v>0.766165612525272</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.9466642702011684</v>
+        <v>0.9417766083065275</v>
       </c>
     </row>
     <row r="25">
@@ -5371,10 +5371,10 @@
         <v>0.175053700169852</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.556707486177727</v>
+        <v>0.8010897848828343</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.09473788152634506</v>
+        <v>0.09825731473948546</v>
       </c>
     </row>
     <row r="26">
@@ -5564,10 +5564,10 @@
         <v>0.1401487264111028</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.5143715252189591</v>
+        <v>0.7653315950284826</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.08629149300262216</v>
+        <v>0.09118727622814662</v>
       </c>
     </row>
     <row r="27">
@@ -5757,10 +5757,10 @@
         <v>0.143369352691572</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.5034925554222136</v>
+        <v>0.7602595020887427</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.06063764663077587</v>
+        <v>0.04890146313376883</v>
       </c>
     </row>
     <row r="28">
@@ -5950,10 +5950,10 @@
         <v>0.4851474053310974</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.3782463573644188</v>
+        <v>0.5313294345715719</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.4529984367538007</v>
+        <v>0.4325256159583578</v>
       </c>
     </row>
     <row r="29">
@@ -6143,10 +6143,10 @@
         <v>0.1139711783212138</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.4148794454667851</v>
+        <v>0.6482058438435977</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.105168634118056</v>
+        <v>0.1301157773176338</v>
       </c>
     </row>
     <row r="30">
@@ -6336,10 +6336,10 @@
         <v>0.3501254266804756</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.3219327785222266</v>
+        <v>0.4015398997076012</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.3869229644604544</v>
+        <v>0.3976206531185572</v>
       </c>
     </row>
     <row r="31">
@@ -6529,10 +6529,10 @@
         <v>0.8435121636384141</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.7458659084776065</v>
+        <v>0.6590991423341728</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.846439933925043</v>
+        <v>0.8508078638493796</v>
       </c>
     </row>
     <row r="32">
@@ -6722,10 +6722,10 @@
         <v>0.9535591403009064</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.889302543719488</v>
+        <v>0.7573739900648613</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.9415301497552694</v>
+        <v>0.9378151477034522</v>
       </c>
     </row>
     <row r="33">
@@ -6915,10 +6915,10 @@
         <v>0.2799397271962683</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.3822409838529274</v>
+        <v>0.3981808496767124</v>
       </c>
       <c r="BK33" t="n">
-        <v>0.3991313141847545</v>
+        <v>0.4146125450592982</v>
       </c>
     </row>
     <row r="34">
@@ -7108,10 +7108,10 @@
         <v>0.1445761712830722</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0.4897604092791417</v>
+        <v>0.682254300787554</v>
       </c>
       <c r="BK34" t="n">
-        <v>0.07058864751422156</v>
+        <v>0.09296030935625581</v>
       </c>
     </row>
     <row r="35">
@@ -7301,10 +7301,10 @@
         <v>0.2294113679937567</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.4973455071037738</v>
+        <v>0.7453100930415859</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.1574841444499442</v>
+        <v>0.1614722846292137</v>
       </c>
     </row>
     <row r="36">
@@ -7494,10 +7494,10 @@
         <v>0.1622419801753585</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.5454783102123951</v>
+        <v>0.7924739617726703</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.08446095219893625</v>
+        <v>0.08937107441632121</v>
       </c>
     </row>
     <row r="37">
@@ -7687,10 +7687,10 @@
         <v>0.9691958042228059</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.8948529347333121</v>
+        <v>0.7671618206452185</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.9519277926027913</v>
+        <v>0.949400783889914</v>
       </c>
     </row>
     <row r="38">
@@ -7880,10 +7880,10 @@
         <v>0.1861918384528494</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.5798923831083432</v>
+        <v>0.8090987377463651</v>
       </c>
       <c r="BK38" t="n">
-        <v>0.1124961604453239</v>
+        <v>0.1152823798670937</v>
       </c>
     </row>
     <row r="39">
@@ -8073,10 +8073,10 @@
         <v>0.172816952679183</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.5525932990316328</v>
+        <v>0.7914594716316045</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.09138528042367856</v>
+        <v>0.0941145276302679</v>
       </c>
     </row>
     <row r="40">
@@ -8266,10 +8266,10 @@
         <v>0.1366079176433218</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0.4497394306943859</v>
+        <v>0.711156378428912</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.06603453691198302</v>
+        <v>0.08915934708546477</v>
       </c>
     </row>
     <row r="41">
@@ -8459,10 +8459,10 @@
         <v>0.1851786589924133</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0.3439636234989526</v>
+        <v>0.5780153338367187</v>
       </c>
       <c r="BK41" t="n">
-        <v>0.2117699467296966</v>
+        <v>0.218635691530973</v>
       </c>
     </row>
     <row r="42">
@@ -8652,10 +8652,10 @@
         <v>0.7514839969279203</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0.5612476549433794</v>
+        <v>0.4906635346399789</v>
       </c>
       <c r="BK42" t="n">
-        <v>0.756874358396505</v>
+        <v>0.7462422482781834</v>
       </c>
     </row>
     <row r="43">
@@ -8845,10 +8845,10 @@
         <v>0.5652506680034247</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.415752886900946</v>
+        <v>0.4718794872154305</v>
       </c>
       <c r="BK43" t="n">
-        <v>0.5838995271437227</v>
+        <v>0.5887835261108709</v>
       </c>
     </row>
     <row r="44">
@@ -9038,10 +9038,10 @@
         <v>0.8771506687191044</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.721338893584758</v>
+        <v>0.6188083146162132</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.8517313992472008</v>
+        <v>0.8497401189315852</v>
       </c>
     </row>
     <row r="45">
@@ -9231,10 +9231,10 @@
         <v>0.08865545736258598</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0.4191751429361871</v>
+        <v>0.6548016927182548</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.1434563557860553</v>
+        <v>0.14713317274091</v>
       </c>
     </row>
     <row r="46">
@@ -9424,10 +9424,10 @@
         <v>0.8344588212901811</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.6731398119085306</v>
+        <v>0.572506103777692</v>
       </c>
       <c r="BK46" t="n">
-        <v>0.8121214153192843</v>
+        <v>0.8115760363660863</v>
       </c>
     </row>
     <row r="47">
@@ -9617,10 +9617,10 @@
         <v>0.08155911967449658</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.4249989675590679</v>
+        <v>0.66256555376961</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.09288458031996344</v>
+        <v>0.1197778730843046</v>
       </c>
     </row>
     <row r="48">
@@ -9810,10 +9810,10 @@
         <v>0.1142366854193543</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.4497542323677365</v>
+        <v>0.6955689875411372</v>
       </c>
       <c r="BK48" t="n">
-        <v>0.07265954298596349</v>
+        <v>0.095019565012831</v>
       </c>
     </row>
     <row r="49">
@@ -10003,10 +10003,10 @@
         <v>0.8154739524585368</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.6617503843931487</v>
+        <v>0.4572044283876087</v>
       </c>
       <c r="BK49" t="n">
-        <v>0.8820182209808112</v>
+        <v>0.8796087458027189</v>
       </c>
     </row>
     <row r="50">
@@ -10196,10 +10196,10 @@
         <v>0.4546204620462045</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.3678203296675719</v>
+        <v>0.464469817932379</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.5352224351406403</v>
+        <v>0.528117776509856</v>
       </c>
     </row>
     <row r="51">
@@ -10389,10 +10389,10 @@
         <v>0.2864370505558765</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.3471883218064462</v>
+        <v>0.4491390697317767</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.3839141285704402</v>
+        <v>0.3832534970855094</v>
       </c>
     </row>
     <row r="52">
@@ -10582,10 +10582,10 @@
         <v>0.2172042680867931</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0.5412627343262859</v>
+        <v>0.7819121766785098</v>
       </c>
       <c r="BK52" t="n">
-        <v>0.162561514352973</v>
+        <v>0.167828101482227</v>
       </c>
     </row>
     <row r="53">
@@ -10775,10 +10775,10 @@
         <v>0.2821801343131108</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.3522407953370785</v>
+        <v>0.5518805779711762</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.3695227898621856</v>
+        <v>0.3643997168875139</v>
       </c>
     </row>
     <row r="54">
@@ -10968,10 +10968,10 @@
         <v>0.123952751414737</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.4739122201900219</v>
+        <v>0.7094082064513961</v>
       </c>
       <c r="BK54" t="n">
-        <v>0.05490712516344982</v>
+        <v>0.06650078333287517</v>
       </c>
     </row>
     <row r="55">
@@ -11161,10 +11161,10 @@
         <v>0.172386746890411</v>
       </c>
       <c r="BJ55" t="n">
-        <v>0.5360783095627827</v>
+        <v>0.7637376302142729</v>
       </c>
       <c r="BK55" t="n">
-        <v>0.08984180016187511</v>
+        <v>0.08965012227501309</v>
       </c>
     </row>
     <row r="56">
@@ -11354,10 +11354,10 @@
         <v>0.922778488978194</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.8365508140900852</v>
+        <v>0.7421586611718342</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.9034284111179919</v>
+        <v>0.9038024874862645</v>
       </c>
     </row>
     <row r="57">
@@ -11547,10 +11547,10 @@
         <v>0.1855476993784636</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.4946356735846625</v>
+        <v>0.7470497125332445</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.1089686047576195</v>
+        <v>0.09726243150365801</v>
       </c>
     </row>
     <row r="58">
@@ -11740,10 +11740,10 @@
         <v>0.1331645515855516</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0.4798161495154237</v>
+        <v>0.7347659829516918</v>
       </c>
       <c r="BK58" t="n">
-        <v>0.09396774481431917</v>
+        <v>0.09551131493524366</v>
       </c>
     </row>
     <row r="59">
@@ -11933,10 +11933,10 @@
         <v>0.07274035273486541</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0.4324397508516056</v>
+        <v>0.7004655246358685</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.07048918791187524</v>
+        <v>0.09243636479938565</v>
       </c>
     </row>
     <row r="60">
@@ -12126,10 +12126,10 @@
         <v>0.1723106897770725</v>
       </c>
       <c r="BJ60" t="n">
-        <v>0.5606740052709295</v>
+        <v>0.7989259632890543</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.100616997696026</v>
+        <v>0.1040699329131675</v>
       </c>
     </row>
     <row r="61">
@@ -12319,10 +12319,10 @@
         <v>0</v>
       </c>
       <c r="BJ61" t="n">
-        <v>0.4411228634850091</v>
+        <v>0.6321992433317745</v>
       </c>
       <c r="BK61" t="n">
-        <v>0.1348533699016944</v>
+        <v>0.1601202337137862</v>
       </c>
     </row>
     <row r="62">
@@ -12332,190 +12332,190 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8126163749580785</v>
+        <v>0.6007713150584472</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7105156500519092</v>
+        <v>0.4439538562426334</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5757575960531872</v>
+        <v>0.4281125412822164</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5810291529141534</v>
+        <v>0.3333806415686714</v>
       </c>
       <c r="F62" t="n">
-        <v>0.503280834611722</v>
+        <v>0.2252135626550993</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3693210387111948</v>
+        <v>0.3434639101494442</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7941310827725341</v>
+        <v>0.5091305539738301</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5784256849028733</v>
+        <v>0.3630207320158721</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8769059414335556</v>
+        <v>0.6621496074165137</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8432888125440029</v>
+        <v>0.5871229431262491</v>
       </c>
       <c r="L62" t="n">
-        <v>0.8541405226390921</v>
+        <v>0.5727087638991687</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5116001284635748</v>
+        <v>0.4772028133611028</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5830186234562988</v>
+        <v>0.8104170651139526</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5626731533732837</v>
+        <v>0.6501217464656187</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4610162540527594</v>
+        <v>0.6320260132683851</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.5255939536785866</v>
+        <v>0.7735846025015206</v>
       </c>
       <c r="R62" t="n">
-        <v>0.5771036939990857</v>
+        <v>0.8040720585337532</v>
       </c>
       <c r="S62" t="n">
-        <v>0.52925271130187</v>
+        <v>0.751593535702188</v>
       </c>
       <c r="T62" t="n">
-        <v>0.4432083344818188</v>
+        <v>0.6857241690110846</v>
       </c>
       <c r="U62" t="n">
-        <v>0.5112923827334412</v>
+        <v>0.7518838901754366</v>
       </c>
       <c r="V62" t="n">
-        <v>0.5511048247580528</v>
+        <v>0.79679102423583</v>
       </c>
       <c r="W62" t="n">
-        <v>0.4182177624849774</v>
+        <v>0.661350932122268</v>
       </c>
       <c r="X62" t="n">
-        <v>0.8901538770551417</v>
+        <v>0.766165612525272</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.556707486177727</v>
+        <v>0.8010897848828343</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.5143715252189591</v>
+        <v>0.7653315950284826</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.5034925554222136</v>
+        <v>0.7602595020887427</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3782463573644188</v>
+        <v>0.5313294345715719</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.4148794454667851</v>
+        <v>0.6482058438435977</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.3219327785222266</v>
+        <v>0.4015398997076012</v>
       </c>
       <c r="AE62" t="n">
-        <v>0.7458659084776065</v>
+        <v>0.6590991423341728</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.889302543719488</v>
+        <v>0.7573739900648613</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.3822409838529274</v>
+        <v>0.3981808496767124</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.4897604092791417</v>
+        <v>0.682254300787554</v>
       </c>
       <c r="AI62" t="n">
-        <v>0.4973455071037738</v>
+        <v>0.7453100930415859</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.5454783102123951</v>
+        <v>0.7924739617726703</v>
       </c>
       <c r="AK62" t="n">
-        <v>0.8948529347333121</v>
+        <v>0.7671618206452185</v>
       </c>
       <c r="AL62" t="n">
-        <v>0.5798923831083432</v>
+        <v>0.8090987377463651</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.5525932990316328</v>
+        <v>0.7914594716316045</v>
       </c>
       <c r="AN62" t="n">
-        <v>0.4497394306943859</v>
+        <v>0.711156378428912</v>
       </c>
       <c r="AO62" t="n">
-        <v>0.3439636234989526</v>
+        <v>0.5780153338367187</v>
       </c>
       <c r="AP62" t="n">
-        <v>0.5612476549433794</v>
+        <v>0.4906635346399789</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.415752886900946</v>
+        <v>0.4718794872154305</v>
       </c>
       <c r="AR62" t="n">
-        <v>0.721338893584758</v>
+        <v>0.6188083146162132</v>
       </c>
       <c r="AS62" t="n">
-        <v>0.4191751429361871</v>
+        <v>0.6548016927182548</v>
       </c>
       <c r="AT62" t="n">
-        <v>0.6731398119085306</v>
+        <v>0.572506103777692</v>
       </c>
       <c r="AU62" t="n">
-        <v>0.4249989675590679</v>
+        <v>0.66256555376961</v>
       </c>
       <c r="AV62" t="n">
-        <v>0.4497542323677365</v>
+        <v>0.6955689875411372</v>
       </c>
       <c r="AW62" t="n">
-        <v>0.6617503843931487</v>
+        <v>0.4572044283876087</v>
       </c>
       <c r="AX62" t="n">
-        <v>0.3678203296675719</v>
+        <v>0.464469817932379</v>
       </c>
       <c r="AY62" t="n">
-        <v>0.3471883218064462</v>
+        <v>0.4491390697317767</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0.5412627343262859</v>
+        <v>0.7819121766785098</v>
       </c>
       <c r="BA62" t="n">
-        <v>0.3522407953370785</v>
+        <v>0.5518805779711762</v>
       </c>
       <c r="BB62" t="n">
-        <v>0.4739122201900219</v>
+        <v>0.7094082064513961</v>
       </c>
       <c r="BC62" t="n">
-        <v>0.5360783095627827</v>
+        <v>0.7637376302142729</v>
       </c>
       <c r="BD62" t="n">
-        <v>0.8365508140900852</v>
+        <v>0.7421586611718342</v>
       </c>
       <c r="BE62" t="n">
-        <v>0.4946356735846625</v>
+        <v>0.7470497125332445</v>
       </c>
       <c r="BF62" t="n">
-        <v>0.4798161495154237</v>
+        <v>0.7347659829516918</v>
       </c>
       <c r="BG62" t="n">
-        <v>0.4324397508516056</v>
+        <v>0.7004655246358685</v>
       </c>
       <c r="BH62" t="n">
-        <v>0.5606740052709295</v>
+        <v>0.7989259632890543</v>
       </c>
       <c r="BI62" t="n">
-        <v>0.4411228634850091</v>
+        <v>0.6321992433317745</v>
       </c>
       <c r="BJ62" t="n">
         <v>0</v>
       </c>
       <c r="BK62" t="n">
-        <v>0.4952354187638183</v>
+        <v>0.7644612097793207</v>
       </c>
     </row>
     <row r="63">
@@ -12525,187 +12525,187 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.965661265609231</v>
+        <v>0.9658225991281506</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8648586204675313</v>
+        <v>0.8703376598188658</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7550440368433465</v>
+        <v>0.7637332265920213</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7588222585992722</v>
+        <v>0.7680467338693502</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7474475440137035</v>
+        <v>0.7540285041162277</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5796524941324501</v>
+        <v>0.5785493928894765</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9238833544581779</v>
+        <v>0.9276382276481304</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7634614999341712</v>
+        <v>0.7693816410829479</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9563912421766991</v>
+        <v>0.9424874577599968</v>
       </c>
       <c r="K63" t="n">
-        <v>0.9585821951327957</v>
+        <v>0.9589827278410081</v>
       </c>
       <c r="L63" t="n">
-        <v>0.9807048317639048</v>
+        <v>0.9801371943952442</v>
       </c>
       <c r="M63" t="n">
-        <v>0.6336615415191472</v>
+        <v>0.6459667350382698</v>
       </c>
       <c r="N63" t="n">
-        <v>0.1150644906859261</v>
+        <v>0.1177723509016278</v>
       </c>
       <c r="O63" t="n">
-        <v>0.3741821563831103</v>
+        <v>0.393633069970706</v>
       </c>
       <c r="P63" t="n">
-        <v>0.605269373365392</v>
+        <v>0.6186684250987838</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.1217062162351357</v>
+        <v>0.1243090843981093</v>
       </c>
       <c r="R63" t="n">
-        <v>0.2259912691954164</v>
+        <v>0.2497463790003698</v>
       </c>
       <c r="S63" t="n">
-        <v>0.108258984302873</v>
+        <v>0.1088983586525853</v>
       </c>
       <c r="T63" t="n">
-        <v>0.4396310455600839</v>
+        <v>0.4193551684938284</v>
       </c>
       <c r="U63" t="n">
-        <v>0.1051970899999074</v>
+        <v>0.1095193965456086</v>
       </c>
       <c r="V63" t="n">
-        <v>0.06984088436525092</v>
+        <v>0.07411361563918045</v>
       </c>
       <c r="W63" t="n">
-        <v>0.2061751512231627</v>
+        <v>0.2059302434166669</v>
       </c>
       <c r="X63" t="n">
-        <v>0.9466642702011684</v>
+        <v>0.9417766083065275</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.09473788152634506</v>
+        <v>0.09825731473948546</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.08629149300262216</v>
+        <v>0.09118727622814662</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.06063764663077587</v>
+        <v>0.04890146313376883</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4529984367538007</v>
+        <v>0.4325256159583578</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.105168634118056</v>
+        <v>0.1301157773176338</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.3869229644604544</v>
+        <v>0.3976206531185572</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.846439933925043</v>
+        <v>0.8508078638493796</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.9415301497552694</v>
+        <v>0.9378151477034522</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.3991313141847545</v>
+        <v>0.4146125450592982</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.07058864751422156</v>
+        <v>0.09296030935625581</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.1574841444499442</v>
+        <v>0.1614722846292137</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.08446095219893625</v>
+        <v>0.08937107441632121</v>
       </c>
       <c r="AK63" t="n">
-        <v>0.9519277926027913</v>
+        <v>0.949400783889914</v>
       </c>
       <c r="AL63" t="n">
-        <v>0.1124961604453239</v>
+        <v>0.1152823798670937</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.09138528042367856</v>
+        <v>0.0941145276302679</v>
       </c>
       <c r="AN63" t="n">
-        <v>0.06603453691198302</v>
+        <v>0.08915934708546477</v>
       </c>
       <c r="AO63" t="n">
-        <v>0.2117699467296966</v>
+        <v>0.218635691530973</v>
       </c>
       <c r="AP63" t="n">
-        <v>0.756874358396505</v>
+        <v>0.7462422482781834</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.5838995271437227</v>
+        <v>0.5887835261108709</v>
       </c>
       <c r="AR63" t="n">
-        <v>0.8517313992472008</v>
+        <v>0.8497401189315852</v>
       </c>
       <c r="AS63" t="n">
-        <v>0.1434563557860553</v>
+        <v>0.14713317274091</v>
       </c>
       <c r="AT63" t="n">
-        <v>0.8121214153192843</v>
+        <v>0.8115760363660863</v>
       </c>
       <c r="AU63" t="n">
-        <v>0.09288458031996344</v>
+        <v>0.1197778730843046</v>
       </c>
       <c r="AV63" t="n">
-        <v>0.07265954298596349</v>
+        <v>0.095019565012831</v>
       </c>
       <c r="AW63" t="n">
-        <v>0.8820182209808112</v>
+        <v>0.8796087458027189</v>
       </c>
       <c r="AX63" t="n">
-        <v>0.5352224351406403</v>
+        <v>0.528117776509856</v>
       </c>
       <c r="AY63" t="n">
-        <v>0.3839141285704402</v>
+        <v>0.3832534970855094</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0.162561514352973</v>
+        <v>0.167828101482227</v>
       </c>
       <c r="BA63" t="n">
-        <v>0.3695227898621856</v>
+        <v>0.3643997168875139</v>
       </c>
       <c r="BB63" t="n">
-        <v>0.05490712516344982</v>
+        <v>0.06650078333287517</v>
       </c>
       <c r="BC63" t="n">
-        <v>0.08984180016187511</v>
+        <v>0.08965012227501309</v>
       </c>
       <c r="BD63" t="n">
-        <v>0.9034284111179919</v>
+        <v>0.9038024874862645</v>
       </c>
       <c r="BE63" t="n">
-        <v>0.1089686047576195</v>
+        <v>0.09726243150365801</v>
       </c>
       <c r="BF63" t="n">
-        <v>0.09396774481431917</v>
+        <v>0.09551131493524366</v>
       </c>
       <c r="BG63" t="n">
-        <v>0.07048918791187524</v>
+        <v>0.09243636479938565</v>
       </c>
       <c r="BH63" t="n">
-        <v>0.100616997696026</v>
+        <v>0.1040699329131675</v>
       </c>
       <c r="BI63" t="n">
-        <v>0.1348533699016944</v>
+        <v>0.1601202337137862</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0.4952354187638183</v>
+        <v>0.7644612097793207</v>
       </c>
       <c r="BK63" t="n">
         <v>0</v>
